--- a/reports/二级子公司C_利润表_2025-02.xlsx
+++ b/reports/二级子公司C_利润表_2025-02.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>77622819</v>
+        <v>79435508</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>75376903</v>
+        <v>75417156</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>150421583</v>
+        <v>151114943</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>352378</v>
+        <v>350974</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>706185</v>
+        <v>700911</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>307556</v>
+        <v>307844</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>616606</v>
+        <v>614361</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>263022</v>
+        <v>264525</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>527308</v>
+        <v>527753</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>245091</v>
+        <v>247419</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>491138</v>
+        <v>493692</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>131209</v>
+        <v>132733</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>262721</v>
+        <v>264994</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>105008</v>
+        <v>106233</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>210047</v>
+        <v>212269</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>76218555</v>
+        <v>78025780</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>73972639</v>
+        <v>74007428</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>70425062</v>
+        <v>70511810</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>140525769</v>
+        <v>141291033</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1058937</v>
+        <v>1055024</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2112676</v>
+        <v>2115067</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>707321</v>
+        <v>701694</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>1411565</v>
+        <v>1406818</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2655373</v>
+        <v>2626671</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>5302694</v>
+        <v>5264254</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>354078</v>
+        <v>349911</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>707736</v>
+        <v>700761</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>265306</v>
+        <v>262475</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>530843</v>
+        <v>525143</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>441372</v>
+        <v>437976</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>883971</v>
+        <v>875366</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>528391</v>
+        <v>526619</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1059005</v>
+        <v>1051568</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2196114</v>
+        <v>2199624</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>4402991</v>
+        <v>4389490</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>49802</v>
+        <v>50115</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>99840</v>
+        <v>99984</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1060619</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>2116429</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>707994</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>1413610</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>52533047</v>
+        <v>56604168</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>46733757</v>
+        <v>46980032</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>45677026</v>
+        <v>45922701</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>91185991</v>
+        <v>91956157</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1056731</v>
+        <v>1057331</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>2108500</v>
+        <v>2118853</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1757788</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>3524059</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>561199</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>1125114</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>350161</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>701722</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>419876</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>840779</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>315002</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>630149</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>210276</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>420214</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>175594</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>350595</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>790348</v>
+        <v>792132</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>1584592</v>
+        <v>1580661</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>613407</v>
+        <v>617609</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>1229662</v>
+        <v>1232182</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>525047</v>
+        <v>530428</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>1051950</v>
+        <v>1058511</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3936272</v>
+        <v>3982867</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>7879627</v>
+        <v>7953178</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>198933</v>
+        <v>177045</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>397815</v>
+        <v>353853</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>348690</v>
+        <v>351768</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>696593</v>
+        <v>703788</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>399404</v>
+        <v>351768</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>797268</v>
+        <v>703788</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>50051</v>
+        <v>50046</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>99864</v>
+        <v>100299</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>179715</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>360306</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>306824</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>615113</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>119354</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>239165</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>89460</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>179117</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>149167</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>298360</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>438179</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>875541</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>79841</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>159396</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>60030</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>119781</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>100291</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>200091</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>70337</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>140372</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>50293</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>100438</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>40235</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>80427</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30146</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>60322</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>23685508</v>
+        <v>22546514</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>27732008</v>
+        <v>25495950</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>175664</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>352192</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>49796</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>99826</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>80479</v>
+        <v>79558</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>160769</v>
+        <v>159406</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>23605029</v>
+        <v>22642620</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2812055</v>
+        <v>2784823</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>5628806</v>
+        <v>5569373</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>20792974</v>
+        <v>19857797</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>20792974</v>
+        <v>19857797</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>20792974</v>
+        <v>19857797</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>20792974</v>
+        <v>19857797</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>20792974</v>
+        <v>19857797</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
